--- a/www/flightdata/xlsx/eoss-349.xlsx
+++ b/www/flightdata/xlsx/eoss-349.xlsx
@@ -3192,7 +3192,7 @@
         <v>30659.53</v>
       </c>
       <c r="I2">
-        <v>552</v>
+        <v>395</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
